--- a/produits/preuves/sortie/c1-adresse/c1-adresse.xlsx
+++ b/produits/preuves/sortie/c1-adresse/c1-adresse.xlsx
@@ -252,6 +252,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="4.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="4.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
